--- a/Received_data/Parafac/data/parafac.xlsx
+++ b/Received_data/Parafac/data/parafac.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,13 +467,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6292974383145107</v>
+        <v>0.623811634571916</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3626532561092006</v>
+        <v>0.01050886960275576</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5957780556778899</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9694192440611927</v>
+        <v>0.5843869431839424</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5981605659169291</v>
+        <v>0.01045877649171538</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4951621387367858</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.525738481628146</v>
+        <v>0.02851159668321872</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2364462185564183</v>
+        <v>0.7453178833611221</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -545,13 +545,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2690309998190661</v>
+        <v>0.7030739584323743</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2877387092958209</v>
+        <v>0.02128103329976057</v>
       </c>
       <c r="D5" t="n">
-        <v>0.240345119579827</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -571,13 +571,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04658056534595652</v>
+        <v>0.3793880851744788</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07961231813451063</v>
+        <v>0.01922583497201271</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07831260253462771</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4506534192646358</v>
+        <v>0.8740319411353803</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4655637766476879</v>
+        <v>0.02513474331895113</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3231232408160088</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -623,13 +623,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5160183137743313</v>
+        <v>0.6838946667827109</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4372897970165202</v>
+        <v>0.01674244360759127</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4532330121509276</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4951425564878135</v>
+        <v>0.8843754050927201</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5440802715127648</v>
+        <v>0.02701684024499543</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3518767583635966</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7509123471241711</v>
+        <v>0.917902195530606</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7346656750451671</v>
+        <v>0.0248720284263716</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5108142663816629</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.408816579681</v>
+        <v>0.6065103916018684</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4088769052069654</v>
+        <v>0.01711677376663052</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4300863440582982</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3087491213376607</v>
+        <v>0.3255227085346189</v>
       </c>
       <c r="C12" t="n">
-        <v>0.07585317645254169</v>
+        <v>0.002774498479618752</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5333514839990621</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6418448299863009</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5641086288591435</v>
+        <v>0.0238754429934621</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3206501064324984</v>
+        <v>0.8111301367422918</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -779,13 +779,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6088565298164966</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5156206064741174</v>
+        <v>0.02316941437823418</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3307398229002759</v>
+        <v>0.8839044107561719</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7003131761883381</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7560547452982561</v>
+        <v>0.02927811948062646</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3317449852069584</v>
+        <v>0.7569757787580408</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2375731173886264</v>
+        <v>0.4673529562703789</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1314653548916373</v>
+        <v>0.007974545381193857</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2957013714955176</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8741515896701034</v>
+        <v>0.8042868945769163</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0.0252090817877911</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7075570178921826</v>
+        <v>1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2548943548179891</v>
+        <v>0.4216660846498688</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1158458948997201</v>
+        <v>0.006108085978273716</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3448743402690822</v>
+        <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7118025515651388</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5668148464850952</v>
+        <v>0.02160758616697619</v>
       </c>
       <c r="D19" t="n">
-        <v>0.361870768411184</v>
+        <v>0.8265943703249533</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5118259787711913</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4182937328920724</v>
+        <v>0.02189254516640738</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2438525990667204</v>
+        <v>0.7606966175597387</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6162271330738301</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6380971591789986</v>
+        <v>0.02773479714408482</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2557085748990369</v>
+        <v>0.6619813686235083</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5129464216573658</v>
+        <v>0.9385864379032883</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4541306351706618</v>
+        <v>0.02308689596727924</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3356837550043293</v>
+        <v>1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4105861364840265</v>
+        <v>0.770132812414021</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2795891257691155</v>
+        <v>0.01493655241048016</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3195066790746462</v>
+        <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8421522204974641</v>
+        <v>0.02240102578796013</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4880902132430691</v>
+        <v>0.7610196534060254</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3882038793270922</v>
+        <v>0.8494561489162806</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2885509954520376</v>
+        <v>0.01759103180157341</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2818557074885343</v>
+        <v>1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6192108295112904</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5509416741443253</v>
+        <v>0.02410000404288556</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3682366991474657</v>
+        <v>0.933923283859045</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4738498240126729</v>
+        <v>0.9714062966162152</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4534177904379865</v>
+        <v>0.02559487921369742</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3051241520880961</v>
+        <v>1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4997393031156913</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.418988609237074</v>
+        <v>0.02299922159651216</v>
       </c>
       <c r="D28" t="n">
-        <v>0.283480905468239</v>
+        <v>0.9245883361858976</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5073563595041009</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3809724109919641</v>
+        <v>0.02009742911201411</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2296533461893643</v>
+        <v>0.7315534769943931</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2025732628674068</v>
+        <v>0.9379905311374535</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1887481526802947</v>
+        <v>0.02382977021568009</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1394486885275351</v>
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3381957979817199</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3334180276690111</v>
+        <v>0.02630300646970625</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1592205310207437</v>
+        <v>0.7305783493181874</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1247,13 +1247,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.423690559365008</v>
+        <v>0.612926288974858</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3484298325973296</v>
+        <v>0.01447681945770661</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4247861906435528</v>
+        <v>1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.3659374547720501</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3537791547118688</v>
+        <v>0.0261611348053478</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2008533700965059</v>
+        <v>0.8631286641534882</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4804720809977034</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4240412499557642</v>
+        <v>0.02398109939782671</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2725201081216919</v>
+        <v>0.9011002448334851</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.3551694333839713</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3176789124307519</v>
+        <v>0.02441267252263726</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2154955649361421</v>
+        <v>0.9621582656059954</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.352670699437159</v>
+        <v>0.684225487001653</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2714414785774431</v>
+        <v>0.01514615572163219</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3119288977180103</v>
+        <v>1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4201911696708275</v>
+        <v>0.9417008953654067</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3757337953737621</v>
+        <v>0.02311971694617787</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2819610587088148</v>
+        <v>1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.3657893860165851</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3575593946704997</v>
+        <v>0.02657448612628243</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2097190254525995</v>
+        <v>0.9037443558914555</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.2385623987284484</v>
+        <v>0.9806920057060765</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2949927916422398</v>
+        <v>0.0329906453379893</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1595367387461961</v>
+        <v>1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.1010739889381717</v>
+        <v>0.4074058741874774</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1076739269798482</v>
+        <v>0.01320693819630369</v>
       </c>
       <c r="D40" t="n">
-        <v>0.150672084611129</v>
+        <v>1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1481,13 +1481,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3347655475479391</v>
+        <v>0.7493633953047105</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3280391386931122</v>
+        <v>0.02077251761046657</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2774270131511918</v>
+        <v>1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4031379944252482</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.343690268814311</v>
+        <v>0.02340043118505815</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2206169774600891</v>
+        <v>0.8921725831845799</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3930966092089683</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3384508036631667</v>
+        <v>0.02382284552476607</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2375257966085015</v>
+        <v>0.9858590382553244</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2274190232038442</v>
+        <v>0.7730026093454488</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2096064915703442</v>
+        <v>0.02016777306781817</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1812513263630182</v>
+        <v>1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3331854550165337</v>
+        <v>0.6969196851340065</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2794278849239734</v>
+        <v>0.01659134721575492</v>
       </c>
       <c r="D45" t="n">
-        <v>0.296018750778193</v>
+        <v>1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2981386349886581</v>
+        <v>0.9013476157592186</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2398123737050208</v>
+        <v>0.02024549774745479</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2038916432542536</v>
+        <v>1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1637,13 +1637,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.19550732040338</v>
+        <v>0.6530691223669629</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1684672317660525</v>
+        <v>0.01620988678091701</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1841363005234352</v>
+        <v>1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1663,13 +1663,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.2987733230664052</v>
+        <v>0.7334965753558796</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2595959640834543</v>
+        <v>0.01804481566352066</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2518802160407233</v>
+        <v>1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1689,13 +1689,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7233054527021907</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5998688397650174</v>
+        <v>0.02243205302936638</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3056754219848887</v>
+        <v>0.6992689931048995</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7070879845652649</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.499184858137055</v>
+        <v>0.01956083594048463</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4141551736846321</v>
+        <v>0.9771394327728498</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.607217107365146</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.436573124010246</v>
+        <v>0.01989784303980447</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3656343926170108</v>
+        <v>0.9970864616049643</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1767,13 +1767,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6464779633338233</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.4666739772361347</v>
+        <v>0.01984530511396407</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3428464710987892</v>
+        <v>0.8848147018493256</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4088719300152405</v>
+        <v>0.7936476005814537</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2566417227815694</v>
+        <v>0.01417963974496306</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3073954913338668</v>
+        <v>1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6203541397610203</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0.4761895573237515</v>
+        <v>0.02115518937930554</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3783518545693965</v>
+        <v>0.9925736484148768</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3991481855902411</v>
+        <v>0.7582539663588205</v>
       </c>
       <c r="C55" t="n">
-        <v>0.27599676840242</v>
+        <v>0.01497679397444053</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3153281810365074</v>
+        <v>1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1871,13 +1871,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5987422017360995</v>
+        <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>0.4917292290303663</v>
+        <v>0.02268250251891551</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3513735851743547</v>
+        <v>0.9636401325304663</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8053737073053983</v>
+        <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6799064121821774</v>
+        <v>0.02293326492789667</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3851211805538757</v>
+        <v>0.7836077678723213</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1923,13 +1923,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5327040297731667</v>
+        <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>0.481864795129911</v>
+        <v>0.02432077946999835</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2154393433162702</v>
+        <v>0.6581194935613763</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1949,13 +1949,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5999508187500366</v>
+        <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.5740776450533489</v>
+        <v>0.02607697664799953</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2846691339882186</v>
+        <v>0.7759420735203385</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1975,13 +1975,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.493475409830412</v>
+        <v>0.8199245313761354</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4777674165943288</v>
+        <v>0.0219111359532178</v>
       </c>
       <c r="D60" t="n">
-        <v>0.383882906466264</v>
+        <v>1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4037158913143123</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>0.3828084568031961</v>
+        <v>0.0259971383706756</v>
       </c>
       <c r="D61" t="n">
-        <v>0.2308356778696913</v>
+        <v>0.9184176917340324</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2027,13 +2027,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4158367039211751</v>
+        <v>0.7094261436865357</v>
       </c>
       <c r="C62" t="n">
-        <v>0.387493169531597</v>
+        <v>0.01851636685973117</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3704112799995192</v>
+        <v>1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4416220477529082</v>
+        <v>0.7485390314840287</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4097337190751722</v>
+        <v>0.0194910291515882</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3695598059688598</v>
+        <v>1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.2685516855279294</v>
+        <v>0.6790098678132434</v>
       </c>
       <c r="C64" t="n">
-        <v>0.28077401524462</v>
+        <v>0.02009933754607918</v>
       </c>
       <c r="D64" t="n">
-        <v>0.2485629206329519</v>
+        <v>1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2105,13 +2105,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4293498700368615</v>
+        <v>0.7185305025982759</v>
       </c>
       <c r="C65" t="n">
-        <v>0.4053162224229094</v>
+        <v>0.01904383824643389</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3754168524029217</v>
+        <v>1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5044191004324514</v>
+        <v>0.8158558870458125</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4345248802550211</v>
+        <v>0.01938307553047863</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3914592767826597</v>
+        <v>1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2157,13 +2157,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5776169247182797</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>0.4626387840513375</v>
+        <v>0.02186486144815349</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3177460883933316</v>
+        <v>0.8933397613203712</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4503463499817454</v>
+        <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4111657131773347</v>
+        <v>0.02459450588090799</v>
       </c>
       <c r="D68" t="n">
-        <v>0.2019717401053702</v>
+        <v>0.7201617397457541</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2209,13 +2209,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.3733446067738971</v>
+        <v>0.9821243144140418</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3679720229130154</v>
+        <v>0.02687873724052719</v>
       </c>
       <c r="D69" t="n">
-        <v>0.2352655624172282</v>
+        <v>1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2235,13 +2235,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.1494973599399041</v>
+        <v>0.1545018155271631</v>
       </c>
       <c r="C70" t="n">
-        <v>0.2046208077635787</v>
+        <v>0.007513909482135744</v>
       </c>
       <c r="D70" t="n">
-        <v>0.5281236719554763</v>
+        <v>1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.2854209055865511</v>
+        <v>0.6413513560341756</v>
       </c>
       <c r="C71" t="n">
-        <v>0.1832357661868914</v>
+        <v>0.01198279699653163</v>
       </c>
       <c r="D71" t="n">
-        <v>0.2660082640525375</v>
+        <v>1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.1853622769513438</v>
+        <v>0.4907950963337208</v>
       </c>
       <c r="C72" t="n">
-        <v>0.2194982094208072</v>
+        <v>0.01711966153428163</v>
       </c>
       <c r="D72" t="n">
-        <v>0.2341058872253786</v>
+        <v>1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2313,13 +2313,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.1410569122035689</v>
+        <v>0.4644073199539741</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1698984361700866</v>
+        <v>0.01674705782735954</v>
       </c>
       <c r="D73" t="n">
-        <v>0.185434595039515</v>
+        <v>1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2339,13 +2339,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.1703352000429602</v>
+        <v>0.4881936632999975</v>
       </c>
       <c r="C74" t="n">
-        <v>0.1967735494826968</v>
+        <v>0.01667066362613384</v>
       </c>
       <c r="D74" t="n">
-        <v>0.2155482803899978</v>
+        <v>1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2365,13 +2365,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.1639603117254342</v>
+        <v>0.5567248531112928</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1885992288361103</v>
+        <v>0.01875423885988878</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1816646238159472</v>
+        <v>1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.1771152374867095</v>
+        <v>0.5086180156848572</v>
       </c>
       <c r="C76" t="n">
-        <v>0.2100732795285566</v>
+        <v>0.01769484340687907</v>
       </c>
       <c r="D76" t="n">
-        <v>0.2166095627178052</v>
+        <v>1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2413,17 +2413,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ADOM-SL8-1-2025</t>
+          <t>ADOM-SL9-1-2025</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.09308936302327696</v>
+        <v>0.2733375989815927</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1270494458008655</v>
+        <v>0.009266253330387756</v>
       </c>
       <c r="D77" t="n">
-        <v>0.09121722304025968</v>
+        <v>1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2432,24 +2432,24 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ADOM-SL8-10-2025</t>
+          <t>ADOM-SL9-10-2025</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.1250200387554153</v>
+        <v>0.8613271504366192</v>
       </c>
       <c r="C78" t="n">
-        <v>0.1601695627310222</v>
+        <v>0.02247377342212831</v>
       </c>
       <c r="D78" t="n">
-        <v>0.1015553877051307</v>
+        <v>1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2458,24 +2458,24 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ADOM-SL8-2-2025</t>
+          <t>ADOM-SL9-11-2025</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.03105689307867146</v>
+        <v>0.9351716109209142</v>
       </c>
       <c r="C79" t="n">
-        <v>0.06011420667191456</v>
+        <v>0.02462990378987115</v>
       </c>
       <c r="D79" t="n">
-        <v>0.07030699563025074</v>
+        <v>1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2484,24 +2484,24 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ADOM-SL8-3-2025</t>
+          <t>ADOM-SL9-12-2025</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.02553781226379662</v>
+        <v>0.7849935525631936</v>
       </c>
       <c r="C80" t="n">
-        <v>0.05000109782840054</v>
+        <v>0.0193226657576061</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0442469103383955</v>
+        <v>1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2510,24 +2510,24 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ADOM-SL8-4-2025</t>
+          <t>ADOM-SL9-13-2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.02894419857531369</v>
+        <v>0.7047028283180609</v>
       </c>
       <c r="C81" t="n">
-        <v>0.05668359899116426</v>
+        <v>0.01646087813372759</v>
       </c>
       <c r="D81" t="n">
-        <v>0.04856854214857732</v>
+        <v>1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2536,24 +2536,24 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ADOM-SL8-5-2025</t>
+          <t>ADOM-SL9-2-2025</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.02238910675054883</v>
+        <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>0.04989238609930599</v>
+        <v>0.01227391984610001</v>
       </c>
       <c r="D82" t="n">
-        <v>0.04135339089597354</v>
+        <v>0.9749065723808018</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2562,24 +2562,24 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ADOM-SL8-6-2025</t>
+          <t>ADOM-SL9-3-2025</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.250588190260506</v>
+        <v>0.7091768419219245</v>
       </c>
       <c r="C83" t="n">
-        <v>0.2432260452980393</v>
+        <v>0.01747748849813362</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2258117677198498</v>
+        <v>1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2588,24 +2588,24 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ADOM-SL8-7-2025</t>
+          <t>ADOM-SL9-4-2025</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.04539865034999625</v>
+        <v>0.7047028283180609</v>
       </c>
       <c r="C84" t="n">
-        <v>0.06615831058224624</v>
+        <v>0.01646087813372759</v>
       </c>
       <c r="D84" t="n">
-        <v>0.05656626817568865</v>
+        <v>1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2614,24 +2614,24 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ADOM-SL8-8-2025</t>
+          <t>ADOM-SL9-5-2025</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.07358473802961191</v>
+        <v>0.6726162579096985</v>
       </c>
       <c r="C85" t="n">
-        <v>0.09353426753557259</v>
+        <v>0.01634692256482707</v>
       </c>
       <c r="D85" t="n">
-        <v>0.05938245785451253</v>
+        <v>1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2640,24 +2640,24 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ADOM-SL8-9-2025</t>
+          <t>ADOM-SL9-6-2025</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.08812136528325269</v>
+        <v>0.6891334185679664</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1081319400160554</v>
+        <v>0.01754288887292919</v>
       </c>
       <c r="D86" t="n">
-        <v>0.07711555754094299</v>
+        <v>1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2666,24 +2666,24 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ADOM-SL9-1-2025</t>
+          <t>ADOM-SL9-7-2025</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.2085389661966377</v>
+        <v>0.817972491046543</v>
       </c>
       <c r="C87" t="n">
-        <v>0.2253445997735045</v>
+        <v>0.02140752442174394</v>
       </c>
       <c r="D87" t="n">
-        <v>0.4563006706910123</v>
+        <v>1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2699,17 +2699,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ADOM-SL9-10-2025</t>
+          <t>ADOM-SL9-8-2025</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.3003002692915862</v>
+        <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>0.2815156770986922</v>
+        <v>0.02248024024947607</v>
       </c>
       <c r="D88" t="n">
-        <v>0.2180854078144034</v>
+        <v>0.9651745598475385</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2725,17 +2725,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ADOM-SL9-11-2025</t>
+          <t>ADOM-SL9-9-2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.3323500108632941</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>0.3163440779111925</v>
+        <v>0.02627753135112414</v>
       </c>
       <c r="D89" t="n">
-        <v>0.2225146379009981</v>
+        <v>0.9601527158223262</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2751,277 +2751,277 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ADOM-SL9-12-2025</t>
+          <t>ADOM-SLB-B-1-2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.2757055271756719</v>
+        <v>0.5554930213251824</v>
       </c>
       <c r="C90" t="n">
-        <v>0.2414356895777341</v>
+        <v>0.02186108531529894</v>
       </c>
       <c r="D90" t="n">
-        <v>0.2180078960224756</v>
+        <v>1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ADOM-SL9-13-2025</t>
+          <t>ADOM-SLB-B-2-2025</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.2549514538838976</v>
+        <v>0.6890684996857616</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2098768725670081</v>
+        <v>0.02537587295852522</v>
       </c>
       <c r="D91" t="n">
-        <v>0.2237614138857671</v>
+        <v>1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ADOM-SL9-2-2025</t>
+          <t>ADOM-SLB-B1-1-2025</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.3878045933207659</v>
+        <v>0.8964126319625784</v>
       </c>
       <c r="C92" t="n">
-        <v>0.175316765070825</v>
+        <v>0.03360026260257666</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2304647336734737</v>
+        <v>1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ADOM-SL9-3-2025</t>
+          <t>ADOM-SLB-B1-2-2025</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.2332360981518333</v>
+        <v>0.8575539444055948</v>
       </c>
       <c r="C93" t="n">
-        <v>0.2028594066211463</v>
+        <v>0.03436021930995069</v>
       </c>
       <c r="D93" t="n">
-        <v>0.2041975837173478</v>
+        <v>1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ADOM-SL9-4-2025</t>
+          <t>ADOM-SLB-B1-3-2025</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.2549514538838976</v>
+        <v>0.4154722498650577</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2098768725670081</v>
+        <v>0.02901603087784603</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2237614138857671</v>
+        <v>1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ADOM-SL9-5-2025</t>
+          <t>ADOM-SLB-B1-4-2025</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.2595021015000975</v>
+        <v>0.844035757480731</v>
       </c>
       <c r="C95" t="n">
-        <v>0.2222181262520526</v>
+        <v>0.03396245044081935</v>
       </c>
       <c r="D95" t="n">
-        <v>0.2411211425823762</v>
+        <v>1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ADOM-SL9-6-2025</t>
+          <t>ADOM-SLB-B1-5-2025</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.2446724612592724</v>
+        <v>0.8544325771621457</v>
       </c>
       <c r="C96" t="n">
-        <v>0.2204260344716258</v>
+        <v>0.03591825379652554</v>
       </c>
       <c r="D96" t="n">
-        <v>0.2228226932700335</v>
+        <v>1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ADOM-SL9-7-2025</t>
+          <t>ADOM-SLB-B1-6-2025</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.3370904153865651</v>
+        <v>0.6530205552741654</v>
       </c>
       <c r="C97" t="n">
-        <v>0.31693314803395</v>
+        <v>0.02664373139320795</v>
       </c>
       <c r="D97" t="n">
-        <v>0.2592937858772864</v>
+        <v>1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ADOM-SL9-8-2025</t>
+          <t>ADOM-SLB-B1-7-2025</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.4145689196800048</v>
+        <v>0.5081076319391521</v>
       </c>
       <c r="C98" t="n">
-        <v>0.3407989123339654</v>
+        <v>0.02142924455756813</v>
       </c>
       <c r="D98" t="n">
-        <v>0.2502841988091952</v>
+        <v>1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ADOM-SL9-9-2025</t>
+          <t>ADOM-SLB-B1-8-2025</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.3895006712384356</v>
+        <v>0.6884917357472374</v>
       </c>
       <c r="C99" t="n">
-        <v>0.3736311848160214</v>
+        <v>0.03122080580758384</v>
       </c>
       <c r="D99" t="n">
-        <v>0.2351919588599154</v>
+        <v>1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B-1-2025</t>
+          <t>ADOM-SLB-B2-1-2025</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.07228684456905193</v>
+        <v>0.3990649353977648</v>
       </c>
       <c r="C100" t="n">
-        <v>0.09853358539153993</v>
+        <v>0.01721236213202471</v>
       </c>
       <c r="D100" t="n">
-        <v>0.08256789562566802</v>
+        <v>1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3037,17 +3037,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B-2-2025</t>
+          <t>ADOM-SLB-B2-3-2025</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.09222356333074831</v>
+        <v>0.2087643774866131</v>
       </c>
       <c r="C101" t="n">
-        <v>0.1206846383769319</v>
+        <v>0.01279810308390329</v>
       </c>
       <c r="D101" t="n">
-        <v>0.0861352935095144</v>
+        <v>1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3063,17 +3063,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-1-2025</t>
+          <t>ADOM-SLB-B3-1-2025</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.06924042342008394</v>
+        <v>0.8031628486731081</v>
       </c>
       <c r="C102" t="n">
-        <v>0.09518327532696425</v>
+        <v>0.0262908646094445</v>
       </c>
       <c r="D102" t="n">
-        <v>0.05178444594789063</v>
+        <v>1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3089,17 +3089,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-2-2025</t>
+          <t>ADOM-SLB-B3-2-2025</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.05983885990619291</v>
+        <v>0.7765977875760738</v>
       </c>
       <c r="C103" t="n">
-        <v>0.08687248838960709</v>
+        <v>0.02554633891636322</v>
       </c>
       <c r="D103" t="n">
-        <v>0.04603644224222839</v>
+        <v>1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3115,17 +3115,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-3-2025</t>
+          <t>ADOM-SLB-B3-3-2025</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.02082717950404163</v>
+        <v>0.6834227738646894</v>
       </c>
       <c r="C104" t="n">
-        <v>0.05094239060602618</v>
+        <v>0.02168982264819541</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0339231670722419</v>
+        <v>1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3141,17 +3141,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-4-2025</t>
+          <t>ADOM-SLB-BO-2-2025</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.06920695350520917</v>
+        <v>0.893823698175803</v>
       </c>
       <c r="C105" t="n">
-        <v>0.1012961097081882</v>
+        <v>0.03119312252366184</v>
       </c>
       <c r="D105" t="n">
-        <v>0.05445566831889912</v>
+        <v>1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3167,17 +3167,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-5-2025</t>
+          <t>ADOM-SLB-BO-3-2025</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.06256298154716039</v>
+        <v>0.7508180377694801</v>
       </c>
       <c r="C106" t="n">
-        <v>0.09583054147276891</v>
+        <v>0.0301113999715199</v>
       </c>
       <c r="D106" t="n">
-        <v>0.04886463240249883</v>
+        <v>1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3185,396 +3185,6 @@
         </is>
       </c>
       <c r="F106" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B1-6-2025</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>0.07159673681154059</v>
-      </c>
-      <c r="C107" t="n">
-        <v>0.1035623886791978</v>
-      </c>
-      <c r="D107" t="n">
-        <v>0.07116179074626879</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B1-7-2025</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>0.06675429967408855</v>
-      </c>
-      <c r="C108" t="n">
-        <v>0.09755709531223332</v>
-      </c>
-      <c r="D108" t="n">
-        <v>0.08437218049135037</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B1-8-2025</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>0.05034271225583026</v>
-      </c>
-      <c r="C109" t="n">
-        <v>0.08165227155081342</v>
-      </c>
-      <c r="D109" t="n">
-        <v>0.04825474805689681</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B2-1-2025</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>0.08015918993714891</v>
-      </c>
-      <c r="C110" t="n">
-        <v>0.1183474084414165</v>
-      </c>
-      <c r="D110" t="n">
-        <v>0.1292842418990987</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B2-3-2025</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>0.05778115535595785</v>
-      </c>
-      <c r="C111" t="n">
-        <v>0.1106180703836584</v>
-      </c>
-      <c r="D111" t="n">
-        <v>0.1661325002046458</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B2_K3_100-2025</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>0.4211417927480994</v>
-      </c>
-      <c r="C112" t="n">
-        <v>0.4415864733952603</v>
-      </c>
-      <c r="D112" t="n">
-        <v>0.5233918984889133</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Mix</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Mix</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B2_K3_150-2025</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>0.5416551327126314</v>
-      </c>
-      <c r="C113" t="n">
-        <v>0.5425740203406594</v>
-      </c>
-      <c r="D113" t="n">
-        <v>0.5840457865161923</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Mix</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Mix</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B2_K3_20-2025</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>0.089280322023138</v>
-      </c>
-      <c r="C114" t="n">
-        <v>0.04964795601602534</v>
-      </c>
-      <c r="D114" t="n">
-        <v>0.07264224948117912</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Mix</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Mix</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B2_K3_40-2025</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>0.2914520428952078</v>
-      </c>
-      <c r="C115" t="n">
-        <v>0.3150870925379659</v>
-      </c>
-      <c r="D115" t="n">
-        <v>0.3393720927321447</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Mix</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Mix</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B2_K3_60-2025</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>0.3320487222732428</v>
-      </c>
-      <c r="C116" t="n">
-        <v>0.35492722191907</v>
-      </c>
-      <c r="D116" t="n">
-        <v>0.3948648757845536</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Mix</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Mix</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B3-1-2025</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>0.1258561381778225</v>
-      </c>
-      <c r="C117" t="n">
-        <v>0.1477258430508749</v>
-      </c>
-      <c r="D117" t="n">
-        <v>0.1000797220583496</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B3-2-2025</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>0.4985765933438753</v>
-      </c>
-      <c r="C118" t="n">
-        <v>0.5835974880210364</v>
-      </c>
-      <c r="D118" t="n">
-        <v>0.4027303067421846</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B3-3-2025</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>0.1029305899458807</v>
-      </c>
-      <c r="C119" t="n">
-        <v>0.1162779815461914</v>
-      </c>
-      <c r="D119" t="n">
-        <v>0.0970102524793984</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-BO-2-2025</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>0.07453256902421611</v>
-      </c>
-      <c r="C120" t="n">
-        <v>0.09543145867283835</v>
-      </c>
-      <c r="D120" t="n">
-        <v>0.05571385281864749</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-BO-3-2025</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>0.06818770650997946</v>
-      </c>
-      <c r="C121" t="n">
-        <v>0.0989040569959081</v>
-      </c>
-      <c r="D121" t="n">
-        <v>0.06039535404862352</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
         <is>
           <t>Baikal</t>
         </is>
